--- a/backend/outputs/RELIANCE.NS_Financial_Model.xlsx
+++ b/backend/outputs/RELIANCE.NS_Financial_Model.xlsx
@@ -923,6 +923,996 @@
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Profitability Margins</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Ratio Analysis'!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Gross Profit Margin (%)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="circle"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Ratio Analysis'!$B$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2021-03-31T00:00:00</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2022-03-31T00:00:00</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023-03-31T00:00:00</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2024-03-31T00:00:00</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2025-03-31T00:00:00</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Ratio Analysis'!$B$2:$F$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>23.60542155258254</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>23.45964788371391</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>25.13306490992871</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>25.08632279906665</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Ratio Analysis'!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>EBITDA Margin (%)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="circle"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Ratio Analysis'!$B$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2021-03-31T00:00:00</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2022-03-31T00:00:00</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023-03-31T00:00:00</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2024-03-31T00:00:00</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2025-03-31T00:00:00</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Ratio Analysis'!$B$3:$F$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>18.15814921195523</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.46421594035326</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>19.63722887608427</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>18.79084848754992</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Ratio Analysis'!$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>EBIT Margin (%)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="circle"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Ratio Analysis'!$B$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2021-03-31T00:00:00</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2022-03-31T00:00:00</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023-03-31T00:00:00</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2024-03-31T00:00:00</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2025-03-31T00:00:00</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Ratio Analysis'!$B$4:$F$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>13.87889873455917</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>12.87303422624981</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>13.99589818259302</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>13.2827749346165</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Ratio Analysis'!$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Net Profit Margin (%)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="circle"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Ratio Analysis'!$B$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2021-03-31T00:00:00</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2022-03-31T00:00:00</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023-03-31T00:00:00</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2024-03-31T00:00:00</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2025-03-31T00:00:00</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Ratio Analysis'!$B$5:$F$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8.722446451894712</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.598466682235272</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7.726532188612574</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7.219706165588431</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:marker val="1"/>
+        <c:axId val="50010001"/>
+        <c:axId val="50010002"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="50010001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="b"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50010002"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="50010002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50010001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Return on Assets &amp; Equity</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Ratio Analysis'!$A$12</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Return on Assets (ROA) (%)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Ratio Analysis'!$B$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2021-03-31T00:00:00</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2022-03-31T00:00:00</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023-03-31T00:00:00</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2024-03-31T00:00:00</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2025-03-31T00:00:00</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Ratio Analysis'!$B$12:$F$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.047904031900458</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.149602689011223</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.964781040395538</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.571470693356976</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Ratio Analysis'!$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Return on Equity (ROE) (%)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Ratio Analysis'!$B$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2021-03-31T00:00:00</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2022-03-31T00:00:00</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023-03-31T00:00:00</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2024-03-31T00:00:00</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2025-03-31T00:00:00</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Ratio Analysis'!$B$10:$F$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7.787834275194519</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.317587501676277</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.774123135903695</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8.259962049335863</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="50020001"/>
+        <c:axId val="50020002"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="50020001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="b"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50020002"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="50020002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50020001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Liquidity Ratios (Current / Quick)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Ratio Analysis'!$A$13</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Current Ratio</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="diamond"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Ratio Analysis'!$B$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2021-03-31T00:00:00</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2022-03-31T00:00:00</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023-03-31T00:00:00</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2024-03-31T00:00:00</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2025-03-31T00:00:00</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Ratio Analysis'!$B$13:$F$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.1242686174521</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.074677252661449</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.183037343312354</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.100351084438783</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Ratio Analysis'!$A$14</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Quick Ratio</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="diamond"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Ratio Analysis'!$B$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2021-03-31T00:00:00</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2022-03-31T00:00:00</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023-03-31T00:00:00</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2024-03-31T00:00:00</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2025-03-31T00:00:00</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Ratio Analysis'!$B$14:$F$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.7750905521249781</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.7208920941115825</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.7985816638019765</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.7784421371851976</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:marker val="1"/>
+        <c:axId val="50030001"/>
+        <c:axId val="50030002"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="50030001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="b"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50030002"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="50030002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50030001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Revenue YoY Growth</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Ratio Analysis'!$A$21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Revenue Growth (%)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="2563EB"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Ratio Analysis'!$B$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2021-03-31T00:00:00</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2022-03-31T00:00:00</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023-03-31T00:00:00</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2024-03-31T00:00:00</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2025-03-31T00:00:00</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Ratio Analysis'!$B$21:$F$21</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>26.13242370643267</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.64616926871224</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7.061540578693637</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="50040001"/>
+        <c:axId val="50040002"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="50040001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="b"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50040002"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="50040002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50040001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>723900</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>723900</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4849,6 +5839,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
